--- a/data_out/country_spreadsheets/Estonia.xlsx
+++ b/data_out/country_spreadsheets/Estonia.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W6"/>
+  <dimension ref="A1:AN6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>17.98</v>
       </c>
+      <c r="X2" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>19.93</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>179.67</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>189.31</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>14.02</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>49.68</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>136.64</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>107.8</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>10.73</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>17.98</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>81.52</v>
       </c>
+      <c r="X3" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>21.57</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2013</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>30.78</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>33.63</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>18.17</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>38.32</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>146.41</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>107.56</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>84.31999999999999</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>107.01</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>108.89</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>98.88</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>81.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>37.15</v>
       </c>
+      <c r="X4" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>24.71</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>190.26</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>58.21</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>95.56999999999999</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>52.39</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>37.15</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>32.21</v>
       </c>
+      <c r="X5" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>25.8</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>28.12</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>22.15</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>205.79</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>152.4</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>68.37</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>139.45</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>123.89</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>32.21</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -927,6 +1216,57 @@
         <v>33.16</v>
       </c>
       <c r="W6" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2021</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>10.77</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>38.99</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>73.34</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>14.82</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>191.15</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>107.06</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>101.56</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>34.27</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>133.78</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>33.16</v>
+      </c>
+      <c r="AN6" t="n">
         <v>20.07</v>
       </c>
     </row>
